--- a/ig/ch-epl/StructureDefinition-productPrice.xlsx
+++ b/ig/ch-epl/StructureDefinition-productPrice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CH - EPL Product Price</t>
+    <t>CH EPL - Product Price</t>
   </si>
   <si>
     <t>Status</t>
